--- a/etf_holdings/2026-10-08_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.18%830,000</t>
+          <t>9.17%830,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>9.17%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.13%1,097,000</t>
+          <t>6.04%1,097,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.73%225,000</t>
+          <t>5.85%225,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.69%375,000</t>
+          <t>5.59%375,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.57%269,000</t>
+          <t>5.47%269,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.97%539,000</t>
+          <t>4.07%539,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.72%387,644</t>
+          <t>3.76%387,644</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.38%116,000</t>
+          <t>3.60%116,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.06%483,000</t>
+          <t>3.09%483,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.98%952,000</t>
+          <t>3.07%952,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1990</v>
+        <v>2360</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.75%323,000</t>
+          <t>2.84%278,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>323000</v>
+        <v>278000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2315</v>
+        <v>1965</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.75%278,000</t>
+          <t>2.75%323,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>278000</v>
+        <v>323000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.70%114,000</t>
+          <t>2.75%114,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:20</t>
+          <t>2026-10-08 23:54:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>-1.85%635</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11790</v>
+        <v>635</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.52%50,000</t>
+          <t>2.46%895,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>50000</v>
+        <v>895000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>647</v>
+        <v>1710</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.48%895,000</t>
+          <t>2.40%324,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>895000</v>
+        <v>324000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1645</v>
+        <v>10615</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.28%324,000</t>
+          <t>2.30%50,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>324000</v>
+        <v>50000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.07%240,000</t>
+          <t>2.15%240,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.68%255,000</t>
+          <t>1.69%255,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-0.83%297.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6845</v>
+        <v>297.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.52%52,000</t>
+          <t>1.50%1,160,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>52000</v>
+        <v>1160000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3140</v>
+        <v>6660</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%113,000</t>
+          <t>1.50%52,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>113000</v>
+        <v>52000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.33%300</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>300</v>
+        <v>2960</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.49%1,160,000</t>
+          <t>1.45%113,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1160000</v>
+        <v>113000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+9.93%3320</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>17750</v>
+        <v>3320</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.28%16,900</t>
+          <t>1.37%95,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>16900</v>
+        <v>95000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.15%3020</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3020</v>
+        <v>17485</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.23%95,000</t>
+          <t>1.28%16,900</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>95000</v>
+        <v>16900</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2455</v>
+        <v>2370</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.18%112,000</t>
+          <t>1.15%112,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2400</v>
+        <v>592</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.08%105,000</t>
+          <t>1.07%418,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>105000</v>
+        <v>418000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-0.98%1010</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>595</v>
+        <v>2330</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.06%418,000</t>
+          <t>1.06%105,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>418000</v>
+        <v>105000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.58%1705</t>
+          <t>-1.17%1685</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1705</v>
+        <v>1685</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:21</t>
+          <t>2026-10-08 23:54:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.94%426,000</t>
+          <t>0.98%426,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.16%2450</t>
+          <t>+0.61%2465</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2450</v>
+        <v>2465</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.84%80,000</t>
+          <t>0.85%80,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.37%185</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>185</v>
+        <v>188.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.70%878,000</t>
+          <t>0.72%878,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.49%529</t>
+          <t>+0.38%531</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.68%302,000</t>
+          <t>0.70%302,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.64%1,350,000</t>
+          <t>0.65%1,350,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1245</v>
+        <v>1285</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.60%113,000</t>
+          <t>0.63%113,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%780</t>
+          <t>+1.03%788</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.57%171,000</t>
+          <t>0.58%171,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.31%1000</t>
+          <t>-2%980</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.31%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.87%287</t>
+          <t>-0.87%284.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.87%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>287</v>
+        <v>284.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.4%1260</t>
+          <t>-0.83%1195</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1260</v>
+        <v>1195</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.30%55,294</t>
+          <t>0.31%59,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>55294</v>
+        <v>59000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.55%1205</t>
+          <t>-0.79%1250</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1205</v>
+        <v>1250</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.30%59,000</t>
+          <t>0.30%55,294</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>59000</v>
+        <v>55294</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.44%2060</t>
+          <t>0%2060</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.35%365</t>
+          <t>-0.68%362.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>365</v>
+        <v>362.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:23</t>
+          <t>2026-10-08 23:54:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.21%3015</t>
+          <t>-3.32%2915</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3015</v>
+        <v>2915</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:24</t>
+          <t>2026-10-08 23:54:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.85%741</t>
+          <t>+1.08%749</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:24</t>
+          <t>2026-10-08 23:54:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.26%605</t>
+          <t>-1.49%596</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:24</t>
+          <t>2026-10-08 23:54:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.13%179.5</t>
+          <t>-1.39%177</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:24</t>
+          <t>2026-10-08 23:54:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+2.93%1230</t>
+          <t>-2.03%1205</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+2.93%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1230</v>
+        <v>1205</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:24</t>
+          <t>2026-10-08 23:54:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%145.5</t>
+          <t>+0.69%146.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
